--- a/podcast/input/queue.xlsx
+++ b/podcast/input/queue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="251">
   <si>
     <t>story</t>
   </si>
@@ -641,6 +641,132 @@
   </si>
   <si>
     <t>podcast/output/story79/story79.mp4</t>
+  </si>
+  <si>
+    <t>podcast/input/story/story80.txt</t>
+  </si>
+  <si>
+    <t>podcast/input/deeplove/deeplove9.mp4; podcast/input/deeplove/deeplove6.mp4; podcast/input/deeplove/deeplove8.mp4; podcast/input/deeplove/deeplove10.mp4; podcast/input/deeplove/deeplove1.mp4; podcast/input/deeplove/deeplove3.mp4; podcast/input/deeplove/deeplove2.mp4; podcast/input/deeplove/deeplove4.mp4; podcast/input/deeplove/deeplove11.mp4; podcast/input/deeplove/deeplove5.mp4; podcast/input/deeplove/deeplove7.mp4</t>
+  </si>
+  <si>
+    <t>podcast/output/story80/story80.mp4</t>
+  </si>
+  <si>
+    <t>podcast/input/story/story81.txt</t>
+  </si>
+  <si>
+    <t>ronaldogoalnew</t>
+  </si>
+  <si>
+    <t>podcast/input/ronaldogoalnew/ronaldogoalnew2.mp4; podcast/input/ronaldogoalnew/ronaldogoalnew1.mp4; podcast/input/ronaldogoalnew/ronaldogoalnew3.mp4</t>
+  </si>
+  <si>
+    <t>podcast/output/story81/story81.mp4</t>
+  </si>
+  <si>
+    <t>podcast/input/story/story82.txt</t>
+  </si>
+  <si>
+    <t>podcast/input/life/life12.mp4; podcast/input/life/life11.mp4; podcast/input/life/life3.mp4; podcast/input/life/life6.mp4; podcast/input/life/life2.mp4; podcast/input/life/life13.mp4; podcast/input/life/life9.mp4; podcast/input/life/life1.mp4; podcast/input/life/life14.mp4; podcast/input/life/life8.mp4; podcast/input/life/life7.mp4</t>
+  </si>
+  <si>
+    <t>podcast/output/story82/story82.mp4</t>
+  </si>
+  <si>
+    <t>podcast/input/story/story83.txt</t>
+  </si>
+  <si>
+    <t>bluelock</t>
+  </si>
+  <si>
+    <t>podcast/input/bluelock/bluelock4.mp4; podcast/input/bluelock/bluelock2.mp4</t>
+  </si>
+  <si>
+    <t>podcast/output/story83/story83.mp4</t>
+  </si>
+  <si>
+    <t>podcast/input/story/story84.txt</t>
+  </si>
+  <si>
+    <t>podcast/input/japanstudent/japanstudent1.mp4; podcast/input/japanstudent/japanstudent2.mp4; podcast/input/japanstudent/japanstudent3.mp4; podcast/input/japanstudent/japanstudent6.mp4; podcast/input/japanstudent/japanstudent7.mp4; podcast/input/japanstudent/japanstudent5.mp4; podcast/input/japanstudent/japanstudent8.mp4; podcast/input/japanstudent/japanstudent4.mp4</t>
+  </si>
+  <si>
+    <t>podcast/output/story84/story84.mp4</t>
+  </si>
+  <si>
+    <t>podcast/input/story/story85.txt</t>
+  </si>
+  <si>
+    <t>podcast/input/aotdemo/aotpeak4.mp4; podcast/input/aotdemo/Video Project 18.mp4; podcast/input/aotdemo/aotdemo3.mp4; podcast/input/aotdemo/aotpeak1.mp4; podcast/input/aotdemo/aotdemo2.mp4</t>
+  </si>
+  <si>
+    <t>podcast/output/story85/story85.mp4</t>
+  </si>
+  <si>
+    <t>podcast/input/story/story86.txt</t>
+  </si>
+  <si>
+    <t>animedemo</t>
+  </si>
+  <si>
+    <t>podcast/input/animedemo/animedemo1.mp4; podcast/input/animedemo/animedemo2.mp4</t>
+  </si>
+  <si>
+    <t>podcast/output/story86/story86.mp4</t>
+  </si>
+  <si>
+    <t>podcast/input/story/story87.txt</t>
+  </si>
+  <si>
+    <t>podcast/input/aotdemo/aotpeak4.mp4; podcast/input/aotdemo/aotdemo2.mp4; podcast/input/aotdemo/aotpeak1.mp4; podcast/input/aotdemo/Video Project 18.mp4; podcast/input/aotdemo/aotdemo3.mp4</t>
+  </si>
+  <si>
+    <t>podcast/output/story87/story87.mp4</t>
+  </si>
+  <si>
+    <t>podcast/input/story/story88.txt</t>
+  </si>
+  <si>
+    <t>japanesenew</t>
+  </si>
+  <si>
+    <t>podcast/input/japanesenew/reelsvideo.io_1782655706212.mp4; podcast/input/japanesenew/reelsvideo.io_1782655766160.mp4; podcast/input/japanesenew/japanesenew2.mp4; podcast/input/japanesenew/japanesenew5.mp4; podcast/input/japanesenew/japanesenew1.mp4; podcast/input/japanesenew/japanesenew4.mp4; podcast/input/japanesenew/reelsvideo.io_1782655703723.mp4; podcast/input/japanesenew/reelsvideo.io_1782655788880.mp4; podcast/input/japanesenew/reelsvideo.io_1782655739472.mp4; podcast/input/japanesenew/japanesenew3.mp4</t>
+  </si>
+  <si>
+    <t>podcast/output/story88/story88.mp4</t>
+  </si>
+  <si>
+    <t>podcast/input/story/story90.txt</t>
+  </si>
+  <si>
+    <t>podcast/input/lifebeauty/lifebeauty1.mp4; podcast/input/lifebeauty/lifebeauty3.mp4; podcast/input/lifebeauty/lifebeauty7.mp4; podcast/input/lifebeauty/lifebeauty9.mp4; podcast/input/lifebeauty/lifebeauty4.mp4; podcast/input/lifebeauty/lifebeauty10.mp4; podcast/input/lifebeauty/lifebeauty5.mp4; podcast/input/lifebeauty/lifebeauty8.mp4; podcast/input/lifebeauty/lifebeauty2.mp4; podcast/input/lifebeauty/lifebeauty6.mp4</t>
+  </si>
+  <si>
+    <t>podcast/output/story89/story89.mp4</t>
+  </si>
+  <si>
+    <t>podcast/input/ronaldo&amp;messi/messiargentina3.mp4; podcast/input/ronaldo&amp;messi/messilastdance1.mp4; podcast/input/ronaldo&amp;messi/ronaldotx5.mp4; podcast/input/ronaldo&amp;messi/ronaldotx1.mp4; podcast/input/ronaldo&amp;messi/ronaldotx2.mp4; podcast/input/ronaldo&amp;messi/ronaldotx16.mp4; podcast/input/ronaldo&amp;messi/messiargentina6.mp4</t>
+  </si>
+  <si>
+    <t>podcast/output/story90/story90.mp4</t>
+  </si>
+  <si>
+    <t>podcast/input/story/story91.txt</t>
+  </si>
+  <si>
+    <t>podcast/input/neymarlastdance/neymarlastdance2.mp4; podcast/input/neymarlastdance/neymarlastdance5.mp4; podcast/input/neymarlastdance/neymarlastdance1.mp4; podcast/input/neymarlastdance/neymarlastdance4.mp4; podcast/input/neymarlastdance/neymarlastdance3.mp4</t>
+  </si>
+  <si>
+    <t>podcast/output/story91/story91.mp4</t>
+  </si>
+  <si>
+    <t>podcast/input/story/story92.txt</t>
+  </si>
+  <si>
+    <t>podcast/input/japanstudent/japanstudent4.mp4; podcast/input/japanstudent/japanstudent8.mp4; podcast/input/japanstudent/japanstudent5.mp4; podcast/input/japanstudent/japanstudent3.mp4; podcast/input/japanstudent/japanstudent2.mp4; podcast/input/japanstudent/japanstudent7.mp4; podcast/input/japanstudent/japanstudent6.mp4; podcast/input/japanstudent/japanstudent1.mp4</t>
+  </si>
+  <si>
+    <t>podcast/output/story92/story92.mp4</t>
   </si>
 </sst>
 </file>
@@ -988,11 +1114,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="27.33203125" customWidth="1"/>
     <col min="2" max="2" width="15.21875" customWidth="1"/>
+    <col min="3" max="3" width="255.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1993,6 +2120,227 @@
         <v>208</v>
       </c>
     </row>
+    <row r="62" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B62" t="s">
+        <v>200</v>
+      </c>
+      <c r="C62" t="s">
+        <v>210</v>
+      </c>
+      <c r="D62" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="63" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B63" t="s">
+        <v>213</v>
+      </c>
+      <c r="C63" t="s">
+        <v>214</v>
+      </c>
+      <c r="D63" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="64" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B64" t="s">
+        <v>163</v>
+      </c>
+      <c r="C64" t="s">
+        <v>217</v>
+      </c>
+      <c r="D64" t="s">
+        <v>8</v>
+      </c>
+      <c r="E64" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="65" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B65" t="s">
+        <v>220</v>
+      </c>
+      <c r="C65" t="s">
+        <v>221</v>
+      </c>
+      <c r="D65" t="s">
+        <v>8</v>
+      </c>
+      <c r="E65" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="66" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B66" t="s">
+        <v>153</v>
+      </c>
+      <c r="C66" t="s">
+        <v>224</v>
+      </c>
+      <c r="D66" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="67" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B67" t="s">
+        <v>104</v>
+      </c>
+      <c r="C67" t="s">
+        <v>227</v>
+      </c>
+      <c r="D67" t="s">
+        <v>8</v>
+      </c>
+      <c r="E67" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="68" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B68" t="s">
+        <v>230</v>
+      </c>
+      <c r="C68" t="s">
+        <v>231</v>
+      </c>
+      <c r="D68" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="69" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B69" t="s">
+        <v>104</v>
+      </c>
+      <c r="C69" t="s">
+        <v>234</v>
+      </c>
+      <c r="D69" t="s">
+        <v>8</v>
+      </c>
+      <c r="E69" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="70" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B70" t="s">
+        <v>237</v>
+      </c>
+      <c r="C70" t="s">
+        <v>238</v>
+      </c>
+      <c r="D70" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="71" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B71" t="s">
+        <v>192</v>
+      </c>
+      <c r="C71" t="s">
+        <v>241</v>
+      </c>
+      <c r="D71" t="s">
+        <v>8</v>
+      </c>
+      <c r="E71" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="72" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B72" t="s">
+        <v>196</v>
+      </c>
+      <c r="C72" t="s">
+        <v>243</v>
+      </c>
+      <c r="D72" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="73" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B73" t="s">
+        <v>127</v>
+      </c>
+      <c r="C73" t="s">
+        <v>246</v>
+      </c>
+      <c r="D73" t="s">
+        <v>8</v>
+      </c>
+      <c r="E73" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="74" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B74" t="s">
+        <v>153</v>
+      </c>
+      <c r="C74" t="s">
+        <v>249</v>
+      </c>
+      <c r="D74" t="s">
+        <v>8</v>
+      </c>
+      <c r="E74" t="s">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/podcast/input/queue.xlsx
+++ b/podcast/input/queue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
   <si>
     <t>story</t>
   </si>
@@ -31,175 +31,79 @@
     <t>result</t>
   </si>
   <si>
-    <t>podcast/input/story/story141.txt</t>
-  </si>
-  <si>
-    <t>krava</t>
-  </si>
-  <si>
-    <t>podcast/input/krava/krava3.mp4; podcast/input/krava/krava8.mp4; podcast/input/krava/krava7.mp4; podcast/input/krava/krava1.mp4; podcast/input/krava/krava6.mp4; podcast/input/krava/krava4.mp4; podcast/input/krava/krava5.mp4; podcast/input/krava/krava2.mp4</t>
+    <t>podcast/input/story/story156.txt</t>
+  </si>
+  <si>
+    <t>peace</t>
+  </si>
+  <si>
+    <t>podcast/input/peace/AQNuWBZCnlvwCkhiw8rZ6eOagH_WurJ8TJcEr_xLF9wWNku4HTbK172bKwSUzic.mp4; podcast/input/peace/AQPo0wN3O5NNEvNZRFisHq4R9rqSN_Tftr4tUkInSiGevhAWRv2ZCk_TC_jw4FE.mp4; podcast/input/peace/AQO9TqdNwu_9k6GFmToyKlUh1MA6k0fE_aRggsg5-YV8B1eu7PoxzachbVGpINDqYZUuMzdG7EOyAUFT5mqr5cVi.mp4; podcast/input/peace/AQMqqdoicV_kBNdCBeZxCPAx4HRA9yE8Za6dyEc6zDb12cFINg0bTYPtsQlWHQj.mp4; podcast/input/peace/AQOOHDz19SdcjCYFub2CD6ZHs1Qr5tu52yKxpNqj_c_CKoWefclsEs_2E2T3QMnc.mp4; podcast/input/peace/AQO8RUWZ0doR1z9GllO0nmrCQMmiMriccV9Iw5MQ9IgoEjB9EEu7u1RMPrBY77c.mp4; podcast/input/peace/AQOq8mCOFRRsecQQu09DuuObRq08Ca3CgPNl8GfJ5WFxHzSLWgKbMLqUsyzU_x4j6cR7oituc.mp4; podcast/input/peace/AQNTftgzHkC5880ZoljiiJy6YIxHmCc_nftxhQCcHy3yX_XWCQD5HG3XMizyHTD.mp4; podcast/input/peace/AQOAxlBeC5Y4S9Wk4feOFVs_Tu_kBcSkrSM1CnFkSqvF_o0BDYmXTCLdHH6L_Eq.mp4; podcast/input/peace/AQPFhocvhfutY5vO_Ksph0sj9NBUYWIGGQwAxG9R_IGOOu1yvGQLoRcoXdT6rJ3.mp4; podcast/input/peace/AQPkHb1YJZ_invN5Ky8eubdr_8fpcO79qjqLvNvjxecRt1ULdNOD6XMV780WwE1bYdFKV0BEkIR.mp4; podcast/input/peace/AQNQVxU7oNKyL9YSEye6_cB9qrfsK_kIxyBW2MqrstensjzClTcAf4_vyDOdHXmLzD.mp4; podcast/input/peace/AQN3ENLuEUeMLoMgI_4e_gLAX0e53oHNZReapwuBU4T7AjItlXloe7r8sStjTtB0vM_0y15Jw5C38U0GGvnbORhbFDOl0iy9SB8upao.mp4; podcast/input/peace/AQMzCOJDvuXfYkiEFDRXdgABuGRZ2wshZcpmuoyn4AYGF-Pc-yqEPftRxR4I9fHf6jr2REaF4yXNp25ZP5FHlEKvGwxnUtSSS3ydjts.mp4; podcast/input/peace/AQNn14KS89xdabJPZSb3BhD044_zXDErEcUtjpGix5QRXe2yjRqgriABY2CIeNI.mp4; podcast/input/peace/AQMWVHJWCpjwx7o5sl6qTEQ0p_Gr6n5mdJq_oQ70ttCUNUe_CBXHPCGxu33a5Zh.mp4</t>
   </si>
   <si>
     <t>Done</t>
   </si>
   <si>
-    <t>podcast/output/story141/story141.mp4</t>
-  </si>
-  <si>
-    <t>podcast/input/story/story142.txt</t>
-  </si>
-  <si>
-    <t>deeplove</t>
-  </si>
-  <si>
-    <t>podcast/input/deeplove/deeplove4.mp4; podcast/input/deeplove/deeplove9.mp4; podcast/input/deeplove/deeplove3.mp4; podcast/input/deeplove/deeplove8.mp4; podcast/input/deeplove/deeplove6.mp4; podcast/input/deeplove/deeplove7.mp4; podcast/input/deeplove/deeplove1.mp4; podcast/input/deeplove/deeplove11.mp4; podcast/input/deeplove/deeplove10.mp4; podcast/input/deeplove/deeplove2.mp4; podcast/input/deeplove/deeplove5.mp4</t>
-  </si>
-  <si>
-    <t>podcast/output/story142/story142.mp4</t>
-  </si>
-  <si>
-    <t>podcast/input/story/story143.txt</t>
-  </si>
-  <si>
-    <t>yamalnew</t>
-  </si>
-  <si>
-    <t>podcast/input/yamalnew/yamalnew4.mp4; podcast/input/yamalnew/yamalnew3.mp4; podcast/input/yamalnew/yamalnew6.mp4; podcast/input/yamalnew/yamalnew2.mp4; podcast/input/yamalnew/yamalnew1.mp4; podcast/input/yamalnew/yamalnew7.mp4; podcast/input/yamalnew/yamalnew5.mp4</t>
-  </si>
-  <si>
-    <t>podcast/output/story143/story143.mp4</t>
-  </si>
-  <si>
-    <t>podcast/input/story/story144.txt</t>
-  </si>
-  <si>
-    <t>mbappetry</t>
-  </si>
-  <si>
-    <t>podcast/input/mbappetry/mbappetry1.mp4; podcast/input/mbappetry/mbappetry2.mp4; podcast/input/mbappetry/mbappetry3.mp4; podcast/input/mbappetry/mbappetry5.mp4; podcast/input/mbappetry/mbappetry4.mp4; podcast/input/mbappetry/mbappetry6.mp4</t>
-  </si>
-  <si>
-    <t>podcast/output/story144/story144.mp4</t>
-  </si>
-  <si>
-    <t>podcast/input/story/story145.txt</t>
-  </si>
-  <si>
-    <t>yourname</t>
-  </si>
-  <si>
-    <t>podcast/input/yourname/yourname1.mp4; podcast/input/yourname/yourname2.mp4</t>
-  </si>
-  <si>
-    <t>podcast/output/story145/story145.mp4</t>
-  </si>
-  <si>
-    <t>podcast/input/story/story146.txt</t>
-  </si>
-  <si>
-    <t>aotdemo</t>
-  </si>
-  <si>
-    <t>podcast/input/aotdemo/aotpeak4.mp4; podcast/input/aotdemo/aotdemo2.mp4; podcast/input/aotdemo/aotpeak1.mp4; podcast/input/aotdemo/Video Project 18.mp4; podcast/input/aotdemo/aotdemo3.mp4</t>
-  </si>
-  <si>
-    <t>podcast/output/story146/story146.mp4</t>
-  </si>
-  <si>
-    <t>podcast/input/story/story147.txt</t>
-  </si>
-  <si>
-    <t>ArminArlert</t>
-  </si>
-  <si>
-    <t>podcast/input/arminarlert/Video_SJc1Une8f7s.mp4</t>
-  </si>
-  <si>
-    <t>podcast/output/story147/story147.mp4</t>
-  </si>
-  <si>
-    <t>podcast/input/story/story148.txt</t>
-  </si>
-  <si>
-    <t>life</t>
-  </si>
-  <si>
-    <t>podcast/input/life/life8.mp4; podcast/input/life/life13.mp4; podcast/input/life/life1.mp4; podcast/input/life/life10.mp4; podcast/input/life/life6.mp4; podcast/input/life/life9.mp4; podcast/input/life/life3.mp4; podcast/input/life/life12.mp4; podcast/input/life/life5.mp4; podcast/input/life/life4.mp4; podcast/input/life/life7.mp4; podcast/input/life/life14.mp4; podcast/input/life/life11.mp4</t>
-  </si>
-  <si>
-    <t>podcast/output/story148/story148.mp4</t>
-  </si>
-  <si>
-    <t>podcast/input/story/story149.txt</t>
-  </si>
-  <si>
-    <t>lifesome</t>
-  </si>
-  <si>
-    <t>podcast/input/lifesome/AQM_9sHL3zzcfU2gMoMLDekSjt9Ro5hcjbRFIYeK74ayJgbjTl1_vahZJM8pFhH.mp4; podcast/input/lifesome/AQOREWT_q1xksrGjnEtoaDV53ZV9s8dvNlDk1ZUcwTatsLqfxmYfqATnfiAGWJw6eMfnN8Z2W3F8u.mp4; podcast/input/lifesome/AQNBoHrhyzpkD2Jh45Owf0BNhHaoMdKXZ4ZdfJK_8knh2QcY4EHIJPVgy91ccGItMMuOMRHhlAH7.mp4; podcast/input/lifesome/AQPKSiPG1ltiBsUjpKXCPE6_mwoHKZn6CfLsKzcWSMx96AwV8GfU0z3j3MY6fhD.mp4; podcast/input/lifesome/AQO6gPMU80f1Spr3ntitoKQ3ySmCWDhrXFzVjJgiXS3W8XMrUDSe6HsM8rw_b1_.mp4; podcast/input/lifesome/AQMo4XfaQsDYBNohmn52UwMrZA229huWLGsyL7fXTJ4mfwS7MQcGQq_60C8yP_9.mp4; podcast/input/lifesome/AQNOrQsaqfD1Khy6A50WAYfwRVnqs2n4kaapKYLDvt6Il5GbuP4wtfkFKc4Zm9I.mp4; podcast/input/lifesome/AQNwhLrfIhTnzSM7_3Tx29iozTYFvPpnGqBy6PDZngiQsSyTclBbfApqevWtTSKg0Kx82tBvOfN70Y.mp4</t>
-  </si>
-  <si>
-    <t>podcast/output/story149/story149.mp4</t>
-  </si>
-  <si>
-    <t>podcast/input/story/story150.txt</t>
-  </si>
-  <si>
-    <t>japanesenew</t>
-  </si>
-  <si>
-    <t>podcast/input/japanesenew/reelsvideo.io_1782655703723.mp4; podcast/input/japanesenew/japanesenew4.mp4; podcast/input/japanesenew/reelsvideo.io_1782655706212.mp4; podcast/input/japanesenew/reelsvideo.io_1782655788880.mp4; podcast/input/japanesenew/japanesenew5.mp4; podcast/input/japanesenew/japanesenew3.mp4; podcast/input/japanesenew/japanesenew2.mp4; podcast/input/japanesenew/japanesenew1.mp4; podcast/input/japanesenew/reelsvideo.io_1782655739472.mp4; podcast/input/japanesenew/reelsvideo.io_1782655766160.mp4</t>
-  </si>
-  <si>
-    <t>podcast/output/story150/story150.mp4</t>
-  </si>
-  <si>
-    <t>podcast/input/story/story151.txt</t>
-  </si>
-  <si>
-    <t>matbiec</t>
-  </si>
-  <si>
-    <t>podcast/input/matbiec/Video Project 32.mp4</t>
-  </si>
-  <si>
-    <t>podcast/output/story151/story151.mp4</t>
-  </si>
-  <si>
-    <t>podcast/input/story/story152.txt</t>
-  </si>
-  <si>
-    <t>alonefootball</t>
-  </si>
-  <si>
-    <t>podcast/input/alonefootball/AQPanzAecI5a47ruLvXARx_xAsWtPWH7V8ctPZ8Wv2f8hY6iQz7_Zj_zUDJ9gMTS7IoopwA.mp4; podcast/input/alonefootball/AQOoQOznhdjyZ5vM48BUdIMEIxfaX0SlcPPe0in3fMFZfucZuPTcjiQ8hPC1xLmsCDcQiwPYpK50.mp4; podcast/input/alonefootball/AQPNFvmR_IQTevJi9SUazcFxOP8szU2gTm0YvrqnyN7SH5AQZl_aFc1ieII0vdYJ5.mp4; podcast/input/alonefootball/AQOZdqBCjFhSbA1Fy2_NBIkA_Ovxo8Mr_pxegkhtJGvOshjZc4t3d4bVcBk4F8b.mp4; podcast/input/alonefootball/AQMk1JLSpELOMbVZ8g1i9IHJzSwooG8vkqn8u5Bsd9LSXjGV7xwNXtW2AbECymeOuLCrDS5N4RI.mp4; podcast/input/alonefootball/AQO4U88WJNi91XipPXrNNaOqW7NM2fersPNQC1p8j_RI3njoZ42KVytDFNkWGl_WLjDZqbR.mp4; podcast/input/alonefootball/AQM4bw8ZmKLc6u8C0FXt9fp4FADbrEjj0rP3cydtvZ5MdLFgYHPuOtCeolzr5I3.mp4</t>
-  </si>
-  <si>
-    <t>podcast/output/story152/story152.mp4</t>
-  </si>
-  <si>
-    <t>podcast/input/story/story153.txt</t>
-  </si>
-  <si>
-    <t>peace</t>
-  </si>
-  <si>
-    <t>podcast/input/peace/AQNn14KS89xdabJPZSb3BhD044_zXDErEcUtjpGix5QRXe2yjRqgriABY2CIeNI.mp4; podcast/input/peace/AQMqqdoicV_kBNdCBeZxCPAx4HRA9yE8Za6dyEc6zDb12cFINg0bTYPtsQlWHQj.mp4; podcast/input/peace/AQMzCOJDvuXfYkiEFDRXdgABuGRZ2wshZcpmuoyn4AYGF-Pc-yqEPftRxR4I9fHf6jr2REaF4yXNp25ZP5FHlEKvGwxnUtSSS3ydjts.mp4; podcast/input/peace/AQOq8mCOFRRsecQQu09DuuObRq08Ca3CgPNl8GfJ5WFxHzSLWgKbMLqUsyzU_x4j6cR7oituc.mp4; podcast/input/peace/AQO9TqdNwu_9k6GFmToyKlUh1MA6k0fE_aRggsg5-YV8B1eu7PoxzachbVGpINDqYZUuMzdG7EOyAUFT5mqr5cVi.mp4; podcast/input/peace/AQOAxlBeC5Y4S9Wk4feOFVs_Tu_kBcSkrSM1CnFkSqvF_o0BDYmXTCLdHH6L_Eq.mp4; podcast/input/peace/AQNTftgzHkC5880ZoljiiJy6YIxHmCc_nftxhQCcHy3yX_XWCQD5HG3XMizyHTD.mp4; podcast/input/peace/AQN3ENLuEUeMLoMgI_4e_gLAX0e53oHNZReapwuBU4T7AjItlXloe7r8sStjTtB0vM_0y15Jw5C38U0GGvnbORhbFDOl0iy9SB8upao.mp4; podcast/input/peace/AQPFhocvhfutY5vO_Ksph0sj9NBUYWIGGQwAxG9R_IGOOu1yvGQLoRcoXdT6rJ3.mp4; podcast/input/peace/AQOOHDz19SdcjCYFub2CD6ZHs1Qr5tu52yKxpNqj_c_CKoWefclsEs_2E2T3QMnc.mp4; podcast/input/peace/AQNuWBZCnlvwCkhiw8rZ6eOagH_WurJ8TJcEr_xLF9wWNku4HTbK172bKwSUzic.mp4; podcast/input/peace/AQPo0wN3O5NNEvNZRFisHq4R9rqSN_Tftr4tUkInSiGevhAWRv2ZCk_TC_jw4FE.mp4; podcast/input/peace/AQPkHb1YJZ_invN5Ky8eubdr_8fpcO79qjqLvNvjxecRt1ULdNOD6XMV780WwE1bYdFKV0BEkIR.mp4; podcast/input/peace/AQNQVxU7oNKyL9YSEye6_cB9qrfsK_kIxyBW2MqrstensjzClTcAf4_vyDOdHXmLzD.mp4; podcast/input/peace/AQO8RUWZ0doR1z9GllO0nmrCQMmiMriccV9Iw5MQ9IgoEjB9EEu7u1RMPrBY77c.mp4; podcast/input/peace/AQMWVHJWCpjwx7o5sl6qTEQ0p_Gr6n5mdJq_oQ70ttCUNUe_CBXHPCGxu33a5Zh.mp4</t>
-  </si>
-  <si>
-    <t>podcast/output/story153/story153.mp4</t>
-  </si>
-  <si>
-    <t>podcast/input/story/story154.txt</t>
-  </si>
-  <si>
-    <t>viewchill</t>
-  </si>
-  <si>
-    <t>podcast/input/viewchill/AQM6XvvbgBsj_NcrzLTRNmPpmJNMkiRPHMt3VZ7FKuI0GilXznzxEPuX0kzXhjDvqZUAvLs9O.mp4; podcast/input/viewchill/AQNVNBZe0HSIZc4L3SGZngopq2nsoToSD1Hdm5Ed4vQgYDQ4qK4gT24KxNYub68.mp4; podcast/input/viewchill/AQODfMqSrRUaxXeXGH2ttYyyMBY_ZWcbM3tTVRHDuZEbbXjPsPZsJtskoBCEJ2IdCDSR0QW.mp4; podcast/input/viewchill/AQMxuSXn_vpVcSzvT4a81XeE3Z9mrdX1EcIKOakGAxvJi1XxMc_mEa6gBBbZ5ei.mp4; podcast/input/viewchill/AQOJFQTsDq22mnCb4NTuD9hVsKXrt0pPic_xyNzPCoqbTko_3r1Ng1FxWtgHBTu.mp4</t>
-  </si>
-  <si>
-    <t>podcast/output/story154/story154.mp4</t>
+    <t>podcast/output/story156/story156.mp4</t>
+  </si>
+  <si>
+    <t>podcast/input/peace/AQN3ENLuEUeMLoMgI_4e_gLAX0e53oHNZReapwuBU4T7AjItlXloe7r8sStjTtB0vM_0y15Jw5C38U0GGvnbORhbFDOl0iy9SB8upao.mp4; podcast/input/peace/AQPo0wN3O5NNEvNZRFisHq4R9rqSN_Tftr4tUkInSiGevhAWRv2ZCk_TC_jw4FE.mp4; podcast/input/peace/AQNuWBZCnlvwCkhiw8rZ6eOagH_WurJ8TJcEr_xLF9wWNku4HTbK172bKwSUzic.mp4; podcast/input/peace/AQO8RUWZ0doR1z9GllO0nmrCQMmiMriccV9Iw5MQ9IgoEjB9EEu7u1RMPrBY77c.mp4; podcast/input/peace/AQMzCOJDvuXfYkiEFDRXdgABuGRZ2wshZcpmuoyn4AYGF-Pc-yqEPftRxR4I9fHf6jr2REaF4yXNp25ZP5FHlEKvGwxnUtSSS3ydjts.mp4; podcast/input/peace/AQOq8mCOFRRsecQQu09DuuObRq08Ca3CgPNl8GfJ5WFxHzSLWgKbMLqUsyzU_x4j6cR7oituc.mp4; podcast/input/peace/AQOAxlBeC5Y4S9Wk4feOFVs_Tu_kBcSkrSM1CnFkSqvF_o0BDYmXTCLdHH6L_Eq.mp4; podcast/input/peace/AQPkHb1YJZ_invN5Ky8eubdr_8fpcO79qjqLvNvjxecRt1ULdNOD6XMV780WwE1bYdFKV0BEkIR.mp4; podcast/input/peace/AQPFhocvhfutY5vO_Ksph0sj9NBUYWIGGQwAxG9R_IGOOu1yvGQLoRcoXdT6rJ3.mp4; podcast/input/peace/AQOOHDz19SdcjCYFub2CD6ZHs1Qr5tu52yKxpNqj_c_CKoWefclsEs_2E2T3QMnc.mp4; podcast/input/peace/AQMWVHJWCpjwx7o5sl6qTEQ0p_Gr6n5mdJq_oQ70ttCUNUe_CBXHPCGxu33a5Zh.mp4; podcast/input/peace/AQNTftgzHkC5880ZoljiiJy6YIxHmCc_nftxhQCcHy3yX_XWCQD5HG3XMizyHTD.mp4; podcast/input/peace/AQMqqdoicV_kBNdCBeZxCPAx4HRA9yE8Za6dyEc6zDb12cFINg0bTYPtsQlWHQj.mp4; podcast/input/peace/AQNn14KS89xdabJPZSb3BhD044_zXDErEcUtjpGix5QRXe2yjRqgriABY2CIeNI.mp4; podcast/input/peace/AQO9TqdNwu_9k6GFmToyKlUh1MA6k0fE_aRggsg5-YV8B1eu7PoxzachbVGpINDqYZUuMzdG7EOyAUFT5mqr5cVi.mp4; podcast/input/peace/AQNQVxU7oNKyL9YSEye6_cB9qrfsK_kIxyBW2MqrstensjzClTcAf4_vyDOdHXmLzD.mp4</t>
+  </si>
+  <si>
+    <t>podcast/input/story/story157.txt</t>
+  </si>
+  <si>
+    <t>manutd</t>
+  </si>
+  <si>
+    <t>podcast/input/manutd/_This_is_Manchester_United_See_you_on_Saturday,_Reds_DcUCfJ.mp4; podcast/input/manutd/AQOtxVqfvk_Zk5hka3Xo73wvxxWpRbIYEvyFWFHMkIhcpBGNAsjJyB9yGD8WMQ2fJc.mp4</t>
+  </si>
+  <si>
+    <t>podcast/output/story157/story157.mp4</t>
+  </si>
+  <si>
+    <t>podcast/input/story/story158.txt</t>
+  </si>
+  <si>
+    <t>love1</t>
+  </si>
+  <si>
+    <t>podcast/input/love1/AQN1c3uPDbItbAd8yy_EG814mdK6kXhEJd76Mxb7AFMuKo8_RowKWpBKHajsk9TYzQWG.mp4; podcast/input/love1/AQOyQE_NK5gp50X_3Kt_JqWON4KjgBeMd5UUQc7KZ4hnr2sSO4em8RzJDBHXf6C.mp4</t>
+  </si>
+  <si>
+    <t>podcast/output/story158/story158.mp4</t>
+  </si>
+  <si>
+    <t>podcast/input/story/story159.txt</t>
+  </si>
+  <si>
+    <t>messinoluc</t>
+  </si>
+  <si>
+    <t>podcast/input/messinoluc/AQMYO1H7RT4LidNhlCYYxRACUWflUePr53LfUxZSLxXrLF0v3I2FhJb42PvDx60.mp4; podcast/input/messinoluc/AQPsYG4Etd7YTFEHkCG61kQ6_im_C8K5bN9zxKtsvUp8Jbzt_847zCJy3iLTJbu.mp4</t>
+  </si>
+  <si>
+    <t>podcast/output/story159/story159.mp4</t>
+  </si>
+  <si>
+    <t>podcast/input/story/story160.txt</t>
+  </si>
+  <si>
+    <t>peace3</t>
+  </si>
+  <si>
+    <t>podcast/input/peace3/Insta_Saver_@jxframes_carousel_DcbQumSlueW_video_7.mp4; podcast/input/peace3/Insta_Saver_@jxframes_carousel_DcbQumSlueW_video_5.mp4; podcast/input/peace3/Insta_Saver_@jxframes_carousel_DcbQumSlueW_video_4.mp4; podcast/input/peace3/AQPHNmJAigMXr1qXYbFmo4ZxVlFYQWMFxumzZZIEj8Gc_Ei39GaRQRuqMvu-FM7whknerluKOUnZUScj5Aj-KD8As0A5jJZsbULoOJ4.mp4; podcast/input/peace3/Insta_Saver_@jxframes_carousel_DcbQumSlueW_video_6.mp4; podcast/input/peace3/AQOJK3Yqu2M3MmUER9sfXu2KxXjqGafHp2y0ZqMF9hYMpPWBW0IMoNWKxI6mR8G.mp4; podcast/input/peace3/AQM7RIUFsBM9zrjINxOuyo8BRwPyNuM5pnaZIWeH7tqIf8Czo9qdxRn1hTUph2X.mp4; podcast/input/peace3/Insta_Saver_@jxframes_carousel_DcbQumSlueW_video_3.mp4; podcast/input/peace3/Insta_Saver_@jxframes_carousel_DcbQumSlueW_video_2.mp4</t>
+  </si>
+  <si>
+    <t>podcast/output/story160/story160.mp4</t>
+  </si>
+  <si>
+    <t>podcast/input/story/story161.txt</t>
+  </si>
+  <si>
+    <t>podcast/input/peace/AQO9TqdNwu_9k6GFmToyKlUh1MA6k0fE_aRggsg5-YV8B1eu7PoxzachbVGpINDqYZUuMzdG7EOyAUFT5mqr5cVi.mp4; podcast/input/peace/AQOq8mCOFRRsecQQu09DuuObRq08Ca3CgPNl8GfJ5WFxHzSLWgKbMLqUsyzU_x4j6cR7oituc.mp4; podcast/input/peace/AQMzCOJDvuXfYkiEFDRXdgABuGRZ2wshZcpmuoyn4AYGF-Pc-yqEPftRxR4I9fHf6jr2REaF4yXNp25ZP5FHlEKvGwxnUtSSS3ydjts.mp4; podcast/input/peace/AQNTftgzHkC5880ZoljiiJy6YIxHmCc_nftxhQCcHy3yX_XWCQD5HG3XMizyHTD.mp4; podcast/input/peace/AQPo0wN3O5NNEvNZRFisHq4R9rqSN_Tftr4tUkInSiGevhAWRv2ZCk_TC_jw4FE.mp4; podcast/input/peace/AQPkHb1YJZ_invN5Ky8eubdr_8fpcO79qjqLvNvjxecRt1ULdNOD6XMV780WwE1bYdFKV0BEkIR.mp4; podcast/input/peace/AQOAxlBeC5Y4S9Wk4feOFVs_Tu_kBcSkrSM1CnFkSqvF_o0BDYmXTCLdHH6L_Eq.mp4; podcast/input/peace/AQMqqdoicV_kBNdCBeZxCPAx4HRA9yE8Za6dyEc6zDb12cFINg0bTYPtsQlWHQj.mp4; podcast/input/peace/AQNn14KS89xdabJPZSb3BhD044_zXDErEcUtjpGix5QRXe2yjRqgriABY2CIeNI.mp4; podcast/input/peace/AQO8RUWZ0doR1z9GllO0nmrCQMmiMriccV9Iw5MQ9IgoEjB9EEu7u1RMPrBY77c.mp4; podcast/input/peace/AQMWVHJWCpjwx7o5sl6qTEQ0p_Gr6n5mdJq_oQ70ttCUNUe_CBXHPCGxu33a5Zh.mp4; podcast/input/peace/AQNQVxU7oNKyL9YSEye6_cB9qrfsK_kIxyBW2MqrstensjzClTcAf4_vyDOdHXmLzD.mp4; podcast/input/peace/AQN3ENLuEUeMLoMgI_4e_gLAX0e53oHNZReapwuBU4T7AjItlXloe7r8sStjTtB0vM_0y15Jw5C38U0GGvnbORhbFDOl0iy9SB8upao.mp4; podcast/input/peace/AQNuWBZCnlvwCkhiw8rZ6eOagH_WurJ8TJcEr_xLF9wWNku4HTbK172bKwSUzic.mp4; podcast/input/peace/AQOOHDz19SdcjCYFub2CD6ZHs1Qr5tu52yKxpNqj_c_CKoWefclsEs_2E2T3QMnc.mp4</t>
+  </si>
+  <si>
+    <t>podcast/output/story161/story161.mp4</t>
   </si>
 </sst>
 </file>
@@ -539,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.5546875" customWidth="1"/>
@@ -564,7 +468,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -583,223 +487,104 @@
     </row>
     <row r="3" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="5" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
         <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="7" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B7" t="s">
         <v>24</v>
       </c>
-      <c r="D6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="C7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
         <v>26</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="8" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>27</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
         <v>28</v>
       </c>
-      <c r="D7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
